--- a/interview/data/audit_issues.xlsx
+++ b/interview/data/audit_issues.xlsx
@@ -9,10 +9,8 @@
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Flagged questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="EMPTY" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DATA-ISSUE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="READ-ONLY" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="OK" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DATA-ISSUE" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="OK" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Flagged questions'!$A$1:$H$121</definedName>
@@ -46,7 +44,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -60,17 +58,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -105,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -116,8 +104,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -550,11 +536,11 @@
         <v>51</v>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-51</t>
         </is>
       </c>
     </row>
@@ -586,13 +572,9 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+8</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -618,11 +600,11 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+62</t>
+          <t>+119</t>
         </is>
       </c>
     </row>
@@ -708,12 +690,12 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
@@ -726,7 +708,11 @@
           <t>Overlapping Shift Detector</t>
         </is>
       </c>
-      <c r="G2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
       <c r="H2" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0038</t>
@@ -744,7 +730,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -788,12 +774,12 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -806,7 +792,11 @@
           <t>Subquery for Exclusion Lists</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
       <c r="H4" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0046</t>
@@ -826,12 +816,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -844,7 +834,11 @@
           <t>Query with NOT IN Clause</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0048</t>
@@ -864,12 +858,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -882,7 +876,11 @@
           <t>Self-Join to Identify Missing Supervisors</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0050</t>
@@ -900,7 +898,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -944,12 +942,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -962,7 +960,11 @@
           <t>Detect Negative Inventory Levels</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0079</t>
@@ -982,12 +984,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1000,7 +1002,11 @@
           <t>Identify Overlapping Project Durations</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0087</t>
@@ -1018,7 +1024,7 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1060,7 +1066,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1104,12 +1110,12 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1122,7 +1128,11 @@
           <t>Duplicate Job Listings</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0094</t>
@@ -1140,7 +1150,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1182,7 +1192,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1224,7 +1234,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1266,7 +1276,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1308,7 +1318,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1352,12 +1362,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1370,7 +1380,11 @@
           <t>Set Operation: EXCEPT</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0126</t>
@@ -1388,7 +1402,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1430,7 +1444,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1474,12 +1488,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1492,7 +1506,11 @@
           <t>Instructor-less Courses Finder</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0142</t>
@@ -1510,7 +1528,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1552,7 +1570,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1594,7 +1612,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1638,12 +1656,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1656,7 +1674,11 @@
           <t>Cross-Sell Opportunity Identifier</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0168</t>
@@ -1674,7 +1696,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1716,7 +1738,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1758,7 +1780,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1800,7 +1822,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1842,7 +1864,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1884,7 +1906,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1926,7 +1948,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1970,12 +1992,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1988,7 +2010,11 @@
           <t>Missing Date Detection in Calendar</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0227</t>
@@ -2008,12 +2034,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -2026,7 +2052,11 @@
           <t>Query to Detect Gaps in Data</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0235</t>
@@ -2046,7 +2076,7 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2064,7 +2094,11 @@
           <t>Calculate Slow Order Durations</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H35" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0251</t>
@@ -2082,7 +2116,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2126,12 +2160,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -2144,7 +2178,11 @@
           <t>Invoice Payment Delay Finder</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0259</t>
@@ -2162,7 +2200,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2204,7 +2242,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2246,7 +2284,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2288,14 +2326,14 @@
           <t>ERR</t>
         </is>
       </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -2310,7 +2348,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
+          <t>OK (4 rows)</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr">
@@ -2332,7 +2370,7 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2352,7 +2390,7 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>no result set</t>
+          <t>OK (6 rows)</t>
         </is>
       </c>
       <c r="H42" s="6" t="inlineStr">
@@ -2372,7 +2410,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2414,7 +2452,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2458,12 +2496,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2476,7 +2514,11 @@
           <t>Repeated Payment Transactions</t>
         </is>
       </c>
-      <c r="G45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H45" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0292</t>
@@ -2496,12 +2538,12 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -2514,7 +2556,11 @@
           <t>Set Operation EXCEPT for Order Comparisons</t>
         </is>
       </c>
-      <c r="G46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H46" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0301</t>
@@ -2534,12 +2580,12 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2552,7 +2598,11 @@
           <t>Identify Overlapping Doctor Appointments</t>
         </is>
       </c>
-      <c r="G47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
       <c r="H47" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0303</t>
@@ -2572,12 +2622,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -2590,7 +2640,11 @@
           <t>Rebuffering Rate by ISP — QoE Analysis</t>
         </is>
       </c>
-      <c r="G48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
       <c r="H48" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0310</t>
@@ -2608,7 +2662,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C49" s="7" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2650,7 +2704,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2692,7 +2746,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2736,7 +2790,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2754,7 +2808,11 @@
           <t>Round-Trip Detection — Same-Day Return Rides</t>
         </is>
       </c>
-      <c r="G52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0325</t>
@@ -2772,7 +2830,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2814,7 +2872,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2856,7 +2914,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2898,7 +2956,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2940,7 +2998,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C57" s="7" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2982,7 +3040,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3024,7 +3082,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C59" s="7" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3066,7 +3124,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3110,7 +3168,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3128,7 +3186,11 @@
           <t>Host Response Time — Median per Listing</t>
         </is>
       </c>
-      <c r="G61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0365</t>
@@ -3146,7 +3208,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3190,12 +3252,12 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -3208,7 +3270,11 @@
           <t>Playlist Engagement — Listens / Saves / Shares</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0371</t>
@@ -3226,7 +3292,7 @@
           <t>EMPTY</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3268,7 +3334,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3310,7 +3376,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3354,12 +3420,12 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -3372,7 +3438,11 @@
           <t>Network Density per Industry — Avg Connections</t>
         </is>
       </c>
-      <c r="G67" s="4" t="inlineStr"/>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0392</t>
@@ -3390,7 +3460,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3434,7 +3504,7 @@
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3452,7 +3522,11 @@
           <t>Lead → Opportunity Conversion Rate by Source</t>
         </is>
       </c>
-      <c r="G69" s="4" t="inlineStr"/>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0404</t>
@@ -3470,7 +3544,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3514,7 +3588,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3532,7 +3606,11 @@
           <t>Sound Virality — Used by 1000+ Creators in 7 Days</t>
         </is>
       </c>
-      <c r="G71" s="4" t="inlineStr"/>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0415</t>
@@ -3552,12 +3630,12 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
@@ -3570,7 +3648,11 @@
           <t>Duet/Stitch Adoption — Original vs Derivative Volume</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0419</t>
@@ -3588,7 +3670,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3630,7 +3712,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3674,12 +3756,12 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -3692,7 +3774,11 @@
           <t>Repeat Customer Rate per Store</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0436</t>
@@ -3710,7 +3796,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3752,7 +3838,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C77" s="7" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3796,12 +3882,12 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -3814,7 +3900,11 @@
           <t>Campaigns With Over 100 Conversions</t>
         </is>
       </c>
-      <c r="G78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H78" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_5-0001</t>
@@ -3834,12 +3924,12 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
@@ -3852,7 +3942,11 @@
           <t>Properties With Over 50 Views in October 2024</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
       <c r="H79" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_5-0004</t>
@@ -3872,12 +3966,12 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -3890,7 +3984,11 @@
           <t>Patients With More Than Two Missed Appointments</t>
         </is>
       </c>
-      <c r="G80" s="4" t="inlineStr"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
       <c r="H80" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_5-0005</t>
@@ -3910,12 +4008,12 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -3928,7 +4026,11 @@
           <t>Find Unique Distance Between Source And Destination-manage Reverse Pair</t>
         </is>
       </c>
-      <c r="G81" s="4" t="inlineStr"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>OK (6 rows)</t>
+        </is>
+      </c>
       <c r="H81" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0010</t>
@@ -3948,12 +4050,12 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
@@ -3966,7 +4068,11 @@
           <t>Customer Order Details</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
       <c r="H82" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0021</t>
@@ -3984,7 +4090,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4028,12 +4134,12 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
@@ -4046,7 +4152,11 @@
           <t>Top Competitors</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H84" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0026</t>
@@ -4066,12 +4176,12 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
@@ -4084,7 +4194,11 @@
           <t>Symmetric Pairs</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
       <c r="H85" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0035</t>
@@ -4102,7 +4216,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4144,7 +4258,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4186,7 +4300,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4230,12 +4344,12 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -4248,7 +4362,11 @@
           <t>Compare Source And Target Table</t>
         </is>
       </c>
-      <c r="G89" s="4" t="inlineStr"/>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
       <c r="H89" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0055</t>
@@ -4268,12 +4386,12 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -4286,7 +4404,11 @@
           <t>Find The Items Which Was Bought Consecutively Three Or More Time</t>
         </is>
       </c>
-      <c r="G90" s="4" t="inlineStr"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H90" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0057</t>
@@ -4304,7 +4426,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C91" s="9" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>DATA-ISSUE</t>
         </is>
@@ -4348,12 +4470,12 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
@@ -4366,7 +4488,11 @@
           <t>Find Avg Order Value Given Customer Placed More Than 5 Orders</t>
         </is>
       </c>
-      <c r="G92" s="4" t="inlineStr"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
       <c r="H92" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0073</t>
@@ -4386,12 +4512,12 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
@@ -4404,7 +4530,11 @@
           <t>Find All Pairs Of Cities Where The Distance Between Them Is Mutual</t>
         </is>
       </c>
-      <c r="G93" s="4" t="inlineStr"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>OK (6 rows)</t>
+        </is>
+      </c>
       <c r="H93" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0089</t>
@@ -4424,12 +4554,12 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -4442,7 +4572,11 @@
           <t>Find All Flights Where At Least Two Passengers Have Confirmed Reservations In Adjacent Seats</t>
         </is>
       </c>
-      <c r="G94" s="4" t="inlineStr"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
       <c r="H94" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0090</t>
@@ -4460,7 +4594,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4504,12 +4638,12 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -4522,7 +4656,11 @@
           <t>Find The Delivery Drivers Who Have Delivered All Types Of Packages Available In The System</t>
         </is>
       </c>
-      <c r="G96" s="4" t="inlineStr"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0092</t>
@@ -4542,7 +4680,7 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -4560,7 +4698,11 @@
           <t>Generate A Report Where You Transform The Data In The Given Format</t>
         </is>
       </c>
-      <c r="G97" s="4" t="inlineStr"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0094</t>
@@ -4578,14 +4720,14 @@
           <t>ERR</t>
         </is>
       </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -4600,7 +4742,7 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
+          <t>OK (2 rows)</t>
         </is>
       </c>
       <c r="H98" s="6" t="inlineStr">
@@ -4620,14 +4762,14 @@
           <t>ERR</t>
         </is>
       </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -4642,7 +4784,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
+          <t>OK (6 rows)</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
@@ -4662,14 +4804,14 @@
           <t>ERR</t>
         </is>
       </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -4684,7 +4826,7 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
+          <t>OK (7 rows)</t>
         </is>
       </c>
       <c r="H100" s="6" t="inlineStr">
@@ -4704,14 +4846,14 @@
           <t>ERR</t>
         </is>
       </c>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -4726,7 +4868,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
+          <t>OK (6 rows)</t>
         </is>
       </c>
       <c r="H101" s="6" t="inlineStr">
@@ -4748,12 +4890,12 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr"/>
@@ -4762,7 +4904,11 @@
           <t>Filter Orders by Date Range</t>
         </is>
       </c>
-      <c r="G102" s="4" t="inlineStr"/>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
       <c r="H102" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0006</t>
@@ -4782,12 +4928,12 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr"/>
@@ -4796,7 +4942,11 @@
           <t>Self-Join to Identify Missing Supervisors</t>
         </is>
       </c>
-      <c r="G103" s="4" t="inlineStr"/>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H103" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0012</t>
@@ -4814,7 +4964,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C104" s="7" t="inlineStr">
+      <c r="C104" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4852,14 +5002,14 @@
           <t>ERR</t>
         </is>
       </c>
-      <c r="C105" s="8" t="inlineStr">
-        <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr"/>
@@ -4870,7 +5020,7 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
+          <t>OK (4 rows)</t>
         </is>
       </c>
       <c r="H105" s="6" t="inlineStr">
@@ -4892,12 +5042,12 @@
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr"/>
@@ -4906,7 +5056,11 @@
           <t>Filter Popular Videos on a Streaming Platform</t>
         </is>
       </c>
-      <c r="G106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
       <c r="H106" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0034</t>
@@ -4924,14 +5078,14 @@
           <t>ERR</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
-        <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr"/>
@@ -4942,7 +5096,7 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
+          <t>OK (4 rows)</t>
         </is>
       </c>
       <c r="H107" s="6" t="inlineStr">
@@ -4964,12 +5118,12 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr"/>
@@ -4978,7 +5132,11 @@
           <t>Filter Funded Startups</t>
         </is>
       </c>
-      <c r="G108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H108" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0128</t>
@@ -4996,7 +5154,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C109" s="7" t="inlineStr">
+      <c r="C109" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5036,12 +5194,12 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr"/>
@@ -5050,7 +5208,11 @@
           <t>Find Duplicate Rows in a Table by Composite Key</t>
         </is>
       </c>
-      <c r="G110" s="4" t="inlineStr"/>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H110" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=practical_40-0021</t>
@@ -5070,12 +5232,12 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr"/>
@@ -5084,7 +5246,11 @@
           <t>Reconcile Two Tables: Find Rows in A Not in B</t>
         </is>
       </c>
-      <c r="G111" s="4" t="inlineStr"/>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>OK (6 rows)</t>
+        </is>
+      </c>
       <c r="H111" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=practical_40-0024</t>
@@ -5102,7 +5268,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C112" s="7" t="inlineStr">
+      <c r="C112" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5142,12 +5308,12 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
@@ -5160,7 +5326,11 @@
           <t>Filter Popular Videos on a Streaming Platform</t>
         </is>
       </c>
-      <c r="G113" s="4" t="inlineStr"/>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
       <c r="H113" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0001</t>
@@ -5178,14 +5348,14 @@
           <t>ERR</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
-        <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
@@ -5200,7 +5370,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
+          <t>OK (4 rows)</t>
         </is>
       </c>
       <c r="H114" s="6" t="inlineStr">
@@ -5220,7 +5390,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C115" s="7" t="inlineStr">
+      <c r="C115" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5262,7 +5432,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C116" s="7" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5306,12 +5476,12 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
@@ -5324,7 +5494,11 @@
           <t>Filter Funded Startups</t>
         </is>
       </c>
-      <c r="G117" s="4" t="inlineStr"/>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
       <c r="H117" s="6" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0036</t>
@@ -5342,7 +5516,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C118" s="7" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5384,7 +5558,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C119" s="7" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5426,7 +5600,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C120" s="7" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5468,7 +5642,7 @@
           <t>DATA-ISSUE</t>
         </is>
       </c>
-      <c r="C121" s="7" t="inlineStr">
+      <c r="C121" s="5" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5633,1965 +5807,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Question Id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Original Issue</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Current Status</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Runtime</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Url</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>co_sql_305-0038</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Overlapping Shift Detector</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0038</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>co_sql_305-0046</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ubisoft</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Subquery for Exclusion Lists</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0046</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>co_sql_305-0048</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Query with NOT IN Clause</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0048</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>co_sql_305-0050</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Self-Join to Identify Missing Supervisors</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0050</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>co_sql_305-0079</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>EPAM</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Detect Negative Inventory Levels</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0079</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>co_sql_305-0087</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Walmart</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Identify Overlapping Project Durations</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0087</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>co_sql_305-0094</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Duplicate Job Listings</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0094</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>co_sql_305-0126</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Citi</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Set Operation: EXCEPT</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0126</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>co_sql_305-0142</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Instructor-less Courses Finder</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0142</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>co_sql_305-0168</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Cross-Sell Opportunity Identifier</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0168</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>co_sql_305-0227</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Reddit</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Missing Date Detection in Calendar</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0227</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>co_sql_305-0235</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Query to Detect Gaps in Data</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0235</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>co_sql_305-0251</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>DoorDash</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Calculate Slow Order Durations</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0251</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>co_sql_305-0259</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Datadog</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Invoice Payment Delay Finder</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0259</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>co_sql_305-0286</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Meta</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Advertiser Status Update</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>no result set</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0286</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>co_sql_305-0292</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Stripe</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Repeated Payment Transactions</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0292</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>co_sql_305-0301</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RedHat</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Set Operation EXCEPT for Order Comparisons</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0301</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>co_sql_305-0303</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Identify Overlapping Doctor Appointments</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0303</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>co_sql_305-0310</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Netflix</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Rebuffering Rate by ISP — QoE Analysis</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0310</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>co_sql_305-0325</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Uber</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Round-Trip Detection — Same-Day Return Rides</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0325</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>co_sql_305-0365</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Airbnb</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Host Response Time — Median per Listing</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0365</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>co_sql_305-0371</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Spotify</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Playlist Engagement — Listens / Saves / Shares</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0371</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>co_sql_305-0392</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Network Density per Industry — Avg Connections</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0392</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>co_sql_305-0404</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Lead → Opportunity Conversion Rate by Source</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0404</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>co_sql_305-0415</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Sound Virality — Used by 1000+ Creators in 7 Days</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0415</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>co_sql_305-0419</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Duet/Stitch Adoption — Original vs Derivative Volume</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0419</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>co_sql_305-0436</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Shopify</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Repeat Customer Rate per Store</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0436</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>community_5-0001</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Campaigns With Over 100 Conversions</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_5-0001</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>community_5-0004</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Properties With Over 50 Views in October 2024</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_5-0004</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>community_5-0005</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Patients With More Than Two Missed Appointments</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_5-0005</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>community_solved-0010</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Find Unique Distance Between Source And Destination-manage Reverse Pair</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0010</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>community_solved-0021</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Customer Order Details</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0021</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>community_solved-0026</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Top Competitors</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0026</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>community_solved-0035</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Symmetric Pairs</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0035</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>community_solved-0055</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Compare Source And Target Table</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0055</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>community_solved-0057</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Find The Items Which Was Bought Consecutively Three Or More Time</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0057</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>community_solved-0073</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Find Avg Order Value Given Customer Placed More Than 5 Orders</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0073</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>community_solved-0089</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Find All Pairs Of Cities Where The Distance Between Them Is Mutual</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0089</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>community_solved-0090</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Find All Flights Where At Least Two Passengers Have Confirmed Reservations In Adjacent Seats</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0090</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>community_solved-0092</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Find The Delivery Drivers Who Have Delivered All Types Of Packages Available In The System</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0092</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>community_solved-0094</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>postgres</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Community</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Generate A Report Where You Transform The Data In The Given Format</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0094</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>mixed_167-0006</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Filter Orders by Date Range</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0006</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>mixed_167-0012</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Self-Join to Identify Missing Supervisors</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0012</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>mixed_167-0034</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Filter Popular Videos on a Streaming Platform</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0034</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>mixed_167-0128</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Filter Funded Startups</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0128</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>practical_40-0021</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Find Duplicate Rows in a Table by Composite Key</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=practical_40-0021</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>practical_40-0024</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Reconcile Two Tables: Find Rows in A Not in B</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=practical_40-0024</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>snowflake_51-0001</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Filter Popular Videos on a Streaming Platform</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0001</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>snowflake_51-0036</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Filter Funded Startups</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0036</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H47" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H48" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId49"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7683,7 +5898,7 @@
           <t>amount_spend(high-null 600/625)</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0063</t>
         </is>
@@ -7697,13 +5912,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7761,752 +5976,348 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>co_sql_305-0280</t>
+          <t>co_sql_305-0038</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Merge Employee and Department Records</t>
+          <t>Overlapping Shift Detector</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0280</t>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0038</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>customer_growth-0006</t>
+          <t>co_sql_305-0039</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>DATA-ISSUE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Nintendo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fraud Signal — More Than 3 Shipping Addresses In a 30-Day Window</t>
+          <t>Sales Territory Performance Evaluator</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=customer_growth-0006</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0039</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>customer_growth-0027</t>
+          <t>co_sql_305-0046</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ubisoft</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Salting a Skewed Aggregation — The Classic Pareto-Distribution Rescue</t>
+          <t>Subquery for Exclusion Lists</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=customer_growth-0027</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0046</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>customer_growth-0028</t>
+          <t>co_sql_305-0048</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DAU / MAU With APPROX_COUNT_DISTINCT — HyperLogLog at Scale</t>
+          <t>Query with NOT IN Clause</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=customer_growth-0028</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0048</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>customer_growth-0029</t>
+          <t>co_sql_305-0050</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Top-3 Products per Customer — QUALIFY Filter on a Window Result</t>
+          <t>Self-Join to Identify Missing Supervisors</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=customer_growth-0029</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0050</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mixed_167-0028</t>
+          <t>co_sql_305-0052</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>DATA-ISSUE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NewRelic</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Merge Employee and Department Records</t>
+          <t>Pivot Data with Aggregate Functions</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0028</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0052</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mixed_167-0127</t>
+          <t>co_sql_305-0079</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>EPAM</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Merge Customer Records from Two Sources</t>
+          <t>Detect Negative Inventory Levels</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0127</t>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0079</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>snowflake_51-0012</t>
+          <t>co_sql_305-0087</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ERR</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>READ-ONLY (tagged non-sqlite)</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>non-sqlite</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lyft</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Merge Customer Records from Two Sources</t>
+          <t>Identify Overlapping Project Durations</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>runtime=non-sqlite, not exercised by PGlite audit</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0012</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H63"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Question Id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Original Issue</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Current Status</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Runtime</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Url</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>co_sql_305-0039</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>DATA-ISSUE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Nintendo</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sales Territory Performance Evaluator</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H2" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0039</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>co_sql_305-0052</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>DATA-ISSUE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NewRelic</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Pivot Data with Aggregate Functions</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H3" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0052</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>co_sql_305-0088</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>EMPTY</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Data Analytics Skills</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>OK (15 rows)</t>
-        </is>
-      </c>
-      <c r="H4" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0088</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>co_sql_305-0091</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DATA-ISSUE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Netflix</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Device Viewership Analysis</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0091</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>co_sql_305-0102</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DATA-ISSUE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>JPMorgan</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Monthly Card Issuance Variance</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0102</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>co_sql_305-0109</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DATA-ISSUE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Year-over-Year Revenue Growth</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0109</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>co_sql_305-0110</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>DATA-ISSUE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Interactive Sales Funnel Analyzer</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0110</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>co_sql_305-0111</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DATA-ISSUE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>DeutscheBank</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Job Application Funnel Analysis</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0111</t>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0087</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>co_sql_305-0120</t>
+          <t>co_sql_305-0088</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -8521,29 +6332,29 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aggregate Data with CUBE</t>
+          <t>Data Analytics Skills</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>OK (24 rows)</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0120</t>
+          <t>OK (15 rows)</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0088</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>co_sql_305-0136</t>
+          <t>co_sql_305-0091</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -8563,12 +6374,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pivot with Aggregate Functions</t>
+          <t>Device Viewership Analysis</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8576,21 +6387,21 @@
           <t>OK (5 rows)</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0136</t>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0091</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>co_sql_305-0140</t>
+          <t>co_sql_305-0094</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -8600,34 +6411,34 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Case Expression in ORDER BY</t>
+          <t>Duplicate Job Listings</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>OK (60 rows)</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0140</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0094</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>co_sql_305-0145</t>
+          <t>co_sql_305-0102</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -8647,29 +6458,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>JPMorgan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Customer Segment Profitability</t>
+          <t>Monthly Card Issuance Variance</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>OK (3 rows)</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0145</t>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0102</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>co_sql_305-0149</t>
+          <t>co_sql_305-0109</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -8689,29 +6500,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pivot with CASE Statements</t>
+          <t>Year-over-Year Revenue Growth</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0149</t>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0109</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>co_sql_305-0167</t>
+          <t>co_sql_305-0110</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -8731,12 +6542,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Quarterly Sales Pivot</t>
+          <t>Interactive Sales Funnel Analyzer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8744,16 +6555,16 @@
           <t>OK (5 rows)</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0167</t>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0110</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>co_sql_305-0169</t>
+          <t>co_sql_305-0111</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -8773,29 +6584,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>DeutscheBank</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Unpivot Regional Product Data</t>
+          <t>Job Application Funnel Analysis</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>OK (100 rows)</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0169</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0111</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>co_sql_305-0170</t>
+          <t>co_sql_305-0120</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8815,34 +6626,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Employee Productivity Trend</t>
+          <t>Aggregate Data with CUBE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0170</t>
+          <t>OK (24 rows)</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0120</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>co_sql_305-0174</t>
+          <t>co_sql_305-0126</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -8852,34 +6663,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Yearly Growth Calculation with LAG</t>
+          <t>Set Operation: EXCEPT</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0174</t>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0126</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>co_sql_305-0175</t>
+          <t>co_sql_305-0136</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8899,29 +6710,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Twitch</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Movie Box Office Trend Analyzer</t>
+          <t>Pivot with Aggregate Functions</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0175</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0136</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>co_sql_305-0179</t>
+          <t>co_sql_305-0140</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8941,34 +6752,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Splunk</t>
+          <t>Robinhood</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GROUPING SETS for Multi-Level Summaries</t>
+          <t>Case Expression in ORDER BY</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>OK (23 rows)</t>
-        </is>
-      </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0179</t>
+          <t>OK (60 rows)</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0140</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>co_sql_305-0189</t>
+          <t>co_sql_305-0142</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -8978,34 +6789,34 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Booking.com</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rolling Average Profit with Window Function</t>
+          <t>Instructor-less Courses Finder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0189</t>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0142</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>co_sql_305-0209</t>
+          <t>co_sql_305-0145</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9025,29 +6836,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Year-on-Year Spend Growth Rate</t>
+          <t>Customer Segment Profitability</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>OK (12 rows)</t>
-        </is>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0209</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0145</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>co_sql_305-0254</t>
+          <t>co_sql_305-0149</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9067,29 +6878,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>COALESCE to Fill Missing Sales Data</t>
+          <t>Pivot with CASE Statements</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0254</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0149</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>co_sql_305-0261</t>
+          <t>co_sql_305-0167</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -9109,34 +6920,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>BMW</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Streaming Subscriber Growth Calculator</t>
+          <t>Quarterly Sales Pivot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0261</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0167</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>co_sql_305-0262</t>
+          <t>co_sql_305-0168</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9146,17 +6957,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flight Delay Pattern Detector</t>
+          <t>Cross-Sell Opportunity Identifier</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9164,16 +6975,16 @@
           <t>OK (5 rows)</t>
         </is>
       </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0262</t>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0168</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>co_sql_305-0269</t>
+          <t>co_sql_305-0169</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -9193,29 +7004,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DigitalOcean</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CTE for Complex Sales Aggregation</t>
+          <t>Unpivot Regional Product Data</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0269</t>
+          <t>OK (100 rows)</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0169</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>co_sql_305-0289</t>
+          <t>co_sql_305-0170</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -9235,29 +7046,29 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pizza Topping Combinations</t>
+          <t>Employee Productivity Trend</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>OK (1359 rows)</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0289</t>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0170</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>co_sql_305-0291</t>
+          <t>co_sql_305-0174</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -9272,34 +7083,34 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monthly Long Call Growth Rate</t>
+          <t>Yearly Growth Calculation with LAG</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>OK (3 rows)</t>
-        </is>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0291</t>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0174</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>co_sql_305-0313</t>
+          <t>co_sql_305-0175</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -9314,34 +7125,34 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Twitch</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Search-then-Play Attribution Within Session</t>
+          <t>Movie Box Office Trend Analyzer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0313</t>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0175</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>co_sql_305-0316</t>
+          <t>co_sql_305-0179</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -9361,29 +7172,29 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Netflix</t>
+          <t>Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Late-Arriving Dimensions — Inferred-Member Pattern</t>
+          <t>GROUPING SETS for Multi-Level Summaries</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>OK (60 rows)</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0316</t>
+          <t>OK (23 rows)</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0179</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>co_sql_305-0320</t>
+          <t>co_sql_305-0189</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -9398,17 +7209,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Driver Utilization Rate — Time-on-Trip / Time-Online</t>
+          <t>Rolling Average Profit with Window Function</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -9416,16 +7227,16 @@
           <t>OK (25 rows)</t>
         </is>
       </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0320</t>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0189</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>co_sql_305-0328</t>
+          <t>co_sql_305-0209</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -9445,34 +7256,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Feed Dwell Time per Post Type</t>
+          <t>Year-on-Year Spend Growth Rate</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0328</t>
+          <t>OK (12 rows)</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0209</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>co_sql_305-0340</t>
+          <t>co_sql_305-0227</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9482,39 +7293,39 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ad Keyword Match-Type ROI</t>
+          <t>Missing Date Detection in Calendar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>OK (4 rows)</t>
-        </is>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0340</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0227</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>co_sql_305-0341</t>
+          <t>co_sql_305-0235</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -9524,7 +7335,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -9534,29 +7345,29 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maps ETA Bias by Travel Mode</t>
+          <t>Query to Detect Gaps in Data</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>OK (4 rows)</t>
-        </is>
-      </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0341</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0235</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>co_sql_305-0342</t>
+          <t>co_sql_305-0251</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -9566,34 +7377,34 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>GA Funnel Drop-Off — Step-to-Step Conversion</t>
+          <t>Calculate Slow Order Durations</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0342</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0251</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>co_sql_305-0344</t>
+          <t>co_sql_305-0254</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -9608,39 +7419,39 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Order Fulfillment SLA — On-Time Delivery %</t>
+          <t>COALESCE to Fill Missing Sales Data</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0344</t>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0254</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>co_sql_305-0346</t>
+          <t>co_sql_305-0259</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -9650,34 +7461,34 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Datadog</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Catalog LAD — ASIN with Late-Arriving Metadata</t>
+          <t>Invoice Payment Delay Finder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>OK (60 rows)</t>
-        </is>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0346</t>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0259</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>co_sql_305-0348</t>
+          <t>co_sql_305-0261</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -9697,29 +7508,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>BMW</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Multi-Warehouse Inventory Routing — Closest-FC Wins</t>
+          <t>Streaming Subscriber Growth Calculator</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>OK (3 rows)</t>
-        </is>
-      </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0348</t>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0261</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>co_sql_305-0354</t>
+          <t>co_sql_305-0262</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9734,34 +7545,34 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Device Upgrade Cycle — Months Between Purchases</t>
+          <t>Flight Delay Pattern Detector</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>OK (23 rows)</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0354</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0262</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>co_sql_305-0366</t>
+          <t>co_sql_305-0269</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9776,39 +7587,39 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>DigitalOcean</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Search-to-Book Funnel by Property Type</t>
+          <t>CTE for Complex Sales Aggregation</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>OK (8 rows)</t>
-        </is>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0366</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0269</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>co_sql_305-0374</t>
+          <t>co_sql_305-0280</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>ERR</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -9818,39 +7629,39 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>Anthropic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Premium Trial Conversion by Country</t>
+          <t>Merge Employee and Department Records</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0374</t>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0280</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>co_sql_305-0378</t>
+          <t>co_sql_305-0286</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -9865,29 +7676,29 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dasher Utilization — Active Time / Online Time</t>
+          <t>Advertiser Status Update</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0378</t>
+          <t>OK (6 rows)</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0286</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>co_sql_305-0379</t>
+          <t>co_sql_305-0289</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9902,7 +7713,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>postgres</t>
+          <t>auto</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -9912,24 +7723,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Delivery Time SLA — Within 30 Minutes</t>
+          <t>Pizza Topping Combinations</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0379</t>
+          <t>OK (1359 rows)</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0289</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>co_sql_305-0397</t>
+          <t>co_sql_305-0291</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9949,34 +7760,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Snap</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Snap Map Active Locations — Per-Hour Density</t>
+          <t>Monthly Long Call Growth Rate</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0397</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0291</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>co_sql_305-0413</t>
+          <t>co_sql_305-0292</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -9986,39 +7797,39 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>Stripe</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>For-You-Page Recommendation Lift — Treatment vs Control</t>
+          <t>Repeated Payment Transactions</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>OK (4 rows)</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0413</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0292</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>co_sql_305-0432</t>
+          <t>co_sql_305-0301</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10028,39 +7839,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>RedHat</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Store GMV by Plan Tier</t>
+          <t>Set Operation EXCEPT for Order Comparisons</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>OK (4 rows)</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0432</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0301</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>co_sql_305-0435</t>
+          <t>co_sql_305-0303</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -10070,39 +7881,39 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Checkout Drop-Off — Step-to-Step Conversion</t>
+          <t>Identify Overlapping Doctor Appointments</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0435</t>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0303</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>co_sql_305-0442</t>
+          <t>co_sql_305-0310</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10117,29 +7928,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stripe</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Payment State Lifecycle — Terminal-State Closure</t>
+          <t>Rebuffering Rate by ISP — QoE Analysis</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>OK (9 rows)</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0442</t>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0310</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>co_sql_305-0443</t>
+          <t>co_sql_305-0313</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -10154,34 +7965,34 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Opportunity Stage Periods — Allowing Backward Transitions</t>
+          <t>Search-then-Play Attribution Within Session</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>OK (9 rows)</t>
-        </is>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0443</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0313</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>community_solved-0023</t>
+          <t>co_sql_305-0316</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -10201,29 +8012,29 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Netflix</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Email Activity Rank</t>
+          <t>Late-Arriving Dimensions — Inferred-Member Pattern</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>OK (8 rows)</t>
-        </is>
-      </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0023</t>
+          <t>OK (60 rows)</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0316</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>community_solved-0042</t>
+          <t>co_sql_305-0320</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -10238,17 +8049,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Write A Query To Get The Running Total Of Quantity For Each Productcode</t>
+          <t>Driver Utilization Rate — Time-on-Trip / Time-Online</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -10256,21 +8067,21 @@
           <t>OK (25 rows)</t>
         </is>
       </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0042</t>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0320</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>community_solved-0046</t>
+          <t>co_sql_305-0325</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -10280,34 +8091,34 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Write SQL To Turn The Columns English, Maths, And Science Into Rows</t>
+          <t>Round-Trip Detection — Same-Day Return Rides</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>OK (75 rows)</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0046</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0325</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>community_solved-0053</t>
+          <t>co_sql_305-0328</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -10327,29 +8138,29 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Meta</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Display The Source Phone Nbr And A Flag Based On The Fisrt And Last Call</t>
+          <t>Feed Dwell Time per Post Type</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>OK (60 rows)</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0053</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0328</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>community_solved-0091</t>
+          <t>co_sql_305-0340</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -10369,29 +8180,29 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Community</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Find The Highest Saleamount For Each Productid Using Correlated Sub Query</t>
+          <t>Ad Keyword Match-Type ROI</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>OK (5 rows)</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0091</t>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0340</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>mixed_167-0013</t>
+          <t>co_sql_305-0341</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10409,27 +8220,31 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Year-over-Year Revenue Growth</t>
+          <t>Maps ETA Bias by Travel Mode</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0013</t>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H55" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0341</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>mixed_167-0131</t>
+          <t>co_sql_305-0342</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10447,27 +8262,31 @@
           <t>auto</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Usage and Accuracy per Model Type</t>
+          <t>GA Funnel Drop-Off — Step-to-Step Conversion</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>OK (8 rows)</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0131</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0342</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>practical_40-0030</t>
+          <t>co_sql_305-0344</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10482,30 +8301,34 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>auto</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Detect Week-Over-Week Changes in a Metric</t>
+          <t>Order Fulfillment SLA — On-Time Delivery %</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>OK (20 rows)</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=practical_40-0030</t>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0344</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>snowflake_51-0014</t>
+          <t>co_sql_305-0346</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10525,29 +8348,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Combine Firms, Funds, and Investments Data</t>
+          <t>Catalog LAD — ASIN with Late-Arriving Metadata</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>OK (125 rows)</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0014</t>
+          <t>OK (60 rows)</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0346</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>snowflake_51-0034</t>
+          <t>co_sql_305-0348</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -10567,29 +8390,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Combine User Interactions</t>
+          <t>Multi-Warehouse Inventory Routing — Closest-FC Wins</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>OK (75 rows)</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0034</t>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0348</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>snowflake_51-0037</t>
+          <t>co_sql_305-0354</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -10604,39 +8427,39 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rank Equipment Maintenance</t>
+          <t>Device Upgrade Cycle — Months Between Purchases</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0037</t>
+          <t>OK (23 rows)</t>
+        </is>
+      </c>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0354</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>snowflake_51-0039</t>
+          <t>co_sql_305-0365</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DATA-ISSUE</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -10646,34 +8469,34 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Detect Self Interactions</t>
+          <t>Host Response Time — Median per Listing</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0039</t>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0365</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>snowflake_51-0044</t>
+          <t>co_sql_305-0366</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10688,67 +8511,2417 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>auto</t>
+          <t>postgres</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Robinhood</t>
+          <t>Airbnb</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Annual GDP Growth Rate</t>
+          <t>Search-to-Book Funnel by Property Type</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>OK (25 rows)</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0044</t>
+          <t>OK (8 rows)</t>
+        </is>
+      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0366</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>co_sql_305-0371</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Playlist Engagement — Listens / Saves / Shares</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0371</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>co_sql_305-0374</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Spotify</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Premium Trial Conversion by Country</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H64" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0374</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>co_sql_305-0378</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Dasher Utilization — Active Time / Online Time</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0378</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>co_sql_305-0379</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Delivery Time SLA — Within 30 Minutes</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H66" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0379</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>co_sql_305-0392</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Network Density per Industry — Avg Connections</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0392</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>co_sql_305-0397</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Snap</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Snap Map Active Locations — Per-Hour Density</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0397</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>co_sql_305-0404</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Lead → Opportunity Conversion Rate by Source</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H69" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0404</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>co_sql_305-0413</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>For-You-Page Recommendation Lift — Treatment vs Control</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0413</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>co_sql_305-0415</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Sound Virality — Used by 1000+ Creators in 7 Days</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H71" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0415</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>co_sql_305-0419</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Duet/Stitch Adoption — Original vs Derivative Volume</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0419</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>co_sql_305-0432</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Store GMV by Plan Tier</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0432</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>co_sql_305-0435</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Checkout Drop-Off — Step-to-Step Conversion</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0435</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>co_sql_305-0436</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Repeat Customer Rate per Store</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0436</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>co_sql_305-0442</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Stripe</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Payment State Lifecycle — Terminal-State Closure</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>OK (9 rows)</t>
+        </is>
+      </c>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0442</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>co_sql_305-0443</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Opportunity Stage Periods — Allowing Backward Transitions</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>OK (9 rows)</t>
+        </is>
+      </c>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=co_sql_305-0443</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>community_5-0001</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Campaigns With Over 100 Conversions</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_5-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>community_5-0004</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Properties With Over 50 Views in October 2024</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_5-0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>community_5-0005</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Patients With More Than Two Missed Appointments</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_5-0005</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>community_solved-0010</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Find Unique Distance Between Source And Destination-manage Reverse Pair</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>OK (6 rows)</t>
+        </is>
+      </c>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0010</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>community_solved-0021</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Customer Order Details</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0021</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>community_solved-0023</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Email Activity Rank</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>OK (8 rows)</t>
+        </is>
+      </c>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0023</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>community_solved-0026</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Top Competitors</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0026</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>community_solved-0035</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Symmetric Pairs</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0035</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>community_solved-0042</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Write A Query To Get The Running Total Of Quantity For Each Productcode</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0042</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>community_solved-0046</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Write SQL To Turn The Columns English, Maths, And Science Into Rows</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>OK (75 rows)</t>
+        </is>
+      </c>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0046</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>community_solved-0053</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Display The Source Phone Nbr And A Flag Based On The Fisrt And Last Call</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>OK (60 rows)</t>
+        </is>
+      </c>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0053</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>community_solved-0055</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Compare Source And Target Table</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0055</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>community_solved-0057</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Find The Items Which Was Bought Consecutively Three Or More Time</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0057</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>community_solved-0073</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Find Avg Order Value Given Customer Placed More Than 5 Orders</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0073</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>community_solved-0089</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Find All Pairs Of Cities Where The Distance Between Them Is Mutual</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>OK (6 rows)</t>
+        </is>
+      </c>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0089</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>community_solved-0090</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Find All Flights Where At Least Two Passengers Have Confirmed Reservations In Adjacent Seats</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0090</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>community_solved-0091</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Find The Highest Saleamount For Each Productid Using Correlated Sub Query</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0091</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>community_solved-0092</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Find The Delivery Drivers Who Have Delivered All Types Of Packages Available In The System</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0092</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>community_solved-0094</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Generate A Report Where You Transform The Data In The Given Format</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=community_solved-0094</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>customer_growth-0006</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ERR</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Fraud Signal — More Than 3 Shipping Addresses In a 30-Day Window</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>OK (2 rows)</t>
+        </is>
+      </c>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=customer_growth-0006</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>customer_growth-0027</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ERR</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Salting a Skewed Aggregation — The Classic Pareto-Distribution Rescue</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>OK (6 rows)</t>
+        </is>
+      </c>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=customer_growth-0027</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>customer_growth-0028</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>ERR</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>DAU / MAU With APPROX_COUNT_DISTINCT — HyperLogLog at Scale</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>OK (7 rows)</t>
+        </is>
+      </c>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=customer_growth-0028</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>customer_growth-0029</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>ERR</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Snowflake</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Top-3 Products per Customer — QUALIFY Filter on a Window Result</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>OK (6 rows)</t>
+        </is>
+      </c>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=customer_growth-0029</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>mixed_167-0006</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Filter Orders by Date Range</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0006</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>mixed_167-0012</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Self-Join to Identify Missing Supervisors</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0012</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>mixed_167-0013</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Year-over-Year Revenue Growth</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>mixed_167-0028</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>ERR</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Merge Employee and Department Records</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0028</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>mixed_167-0034</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Filter Popular Videos on a Streaming Platform</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0034</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>mixed_167-0127</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ERR</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Merge Customer Records from Two Sources</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0127</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>mixed_167-0128</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Filter Funded Startups</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0128</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>mixed_167-0131</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Usage and Accuracy per Model Type</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>OK (8 rows)</t>
+        </is>
+      </c>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=mixed_167-0131</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>practical_40-0021</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Find Duplicate Rows in a Table by Composite Key</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=practical_40-0021</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>practical_40-0024</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Reconcile Two Tables: Find Rows in A Not in B</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>OK (6 rows)</t>
+        </is>
+      </c>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=practical_40-0024</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>practical_40-0030</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Detect Week-Over-Week Changes in a Metric</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>OK (20 rows)</t>
+        </is>
+      </c>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=practical_40-0030</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>snowflake_51-0001</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Filter Popular Videos on a Streaming Platform</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>OK (5 rows)</t>
+        </is>
+      </c>
+      <c r="H112" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>snowflake_51-0012</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ERR</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Lyft</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Merge Customer Records from Two Sources</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>OK (4 rows)</t>
+        </is>
+      </c>
+      <c r="H113" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0012</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>snowflake_51-0014</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Combine Firms, Funds, and Investments Data</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>OK (125 rows)</t>
+        </is>
+      </c>
+      <c r="H114" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0014</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>snowflake_51-0034</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Combine User Interactions</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>OK (75 rows)</t>
+        </is>
+      </c>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0034</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>snowflake_51-0036</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>postgres</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Filter Funded Startups</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>OK (3 rows)</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0036</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>snowflake_51-0037</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Rank Equipment Maintenance</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0037</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>snowflake_51-0039</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Detect Self Interactions</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0039</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>snowflake_51-0044</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>auto</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Robinhood</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Annual GDP Growth Rate</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>OK (25 rows)</t>
+        </is>
+      </c>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0044</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>snowflake_51-0046</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>DATA-ISSUE</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>DATA-ISSUE</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>Materials Experiment Records</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>OK (25 rows)</t>
         </is>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="H120" s="8" t="inlineStr">
         <is>
           <t>https://paddyspeaks.com/interview.app/sql.html?q=snowflake_51-0046</t>
         </is>
@@ -10818,6 +10991,63 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H120" r:id="rId119"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/interview/data/audit_issues.xlsx
+++ b/interview/data/audit_issues.xlsx
@@ -1550,7 +1550,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>OK (3 rows)</t>
+          <t>OK (2 rows)</t>
         </is>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>OK (3 rows)</t>
+          <t>OK (5 rows)</t>
         </is>
       </c>
       <c r="H59" s="6" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>OK (3 rows)</t>
+          <t>OK (2 rows)</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>OK (3 rows)</t>
+          <t>OK (5 rows)</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
